--- a/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar30_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_epem_a0.10_b0.10_chibar30_Q10_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009757273840075886</v>
+        <v>0.00982784365362011</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009757273840075886</v>
+        <v>0.00982784365362011</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004436694180936062</v>
+        <v>0.005120429496243174</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009679137348960013</v>
+        <v>0.009713577185626286</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009679137348960013</v>
+        <v>0.009713577185626286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004095962780858444</v>
+        <v>0.004638081657238585</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00952920509644588</v>
+        <v>0.009514518982732093</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00952920509644588</v>
+        <v>0.009514518982732093</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003835036751814051</v>
+        <v>0.004215842253624402</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.009265794448792183</v>
+        <v>0.009198888091324487</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009265794448792183</v>
+        <v>0.009198888091324487</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003596434342625258</v>
+        <v>0.003867869311695742</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.008996929854604475</v>
+        <v>0.008887345357747911</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008996929854604475</v>
+        <v>0.008887345357747911</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003344080648386573</v>
+        <v>0.003571272062640773</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.008791693536712712</v>
+        <v>0.008655576820523803</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008791693536712712</v>
+        <v>0.008655576820523803</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003068518676224711</v>
+        <v>0.003286360355489003</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008681447114557166</v>
+        <v>0.00853557277610336</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008681447114557166</v>
+        <v>0.00853557277610336</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002779725019740564</v>
+        <v>0.002996418395413954</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008701732139704288</v>
+        <v>0.008561794471068626</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008701732139704288</v>
+        <v>0.008561794471068626</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002518122579710192</v>
+        <v>0.002741380041582539</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.008818648876960643</v>
+        <v>0.008698351841807412</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008818648876960643</v>
+        <v>0.008698351841807412</v>
       </c>
       <c r="D10" t="n">
-        <v>0.002326427022731734</v>
+        <v>0.002578753000903396</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.009262240481902115</v>
+        <v>0.009173819273107793</v>
       </c>
       <c r="C11" t="n">
-        <v>0.009262240481902115</v>
+        <v>0.009173819273107793</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002245992467973462</v>
+        <v>0.002559514299955346</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009888835646504619</v>
+        <v>0.009841990968241603</v>
       </c>
       <c r="C12" t="n">
-        <v>0.009888835646504619</v>
+        <v>0.009841990968241603</v>
       </c>
       <c r="D12" t="n">
-        <v>0.002248511231582764</v>
+        <v>0.002650441240269969</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01078259788122849</v>
+        <v>0.01078578317937964</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01078259788122849</v>
+        <v>0.01078578317937964</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00229453227509303</v>
+        <v>0.002777284113672659</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01201404396023003</v>
+        <v>0.012075110566619</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01201404396023003</v>
+        <v>0.012075110566619</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002329076324718691</v>
+        <v>0.002866426161208374</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01347720847538758</v>
+        <v>0.01360008942061512</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01347720847538758</v>
+        <v>0.01360008942061512</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002326864525634703</v>
+        <v>0.002868963444142697</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01520189306132939</v>
+        <v>0.01538820876819236</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01520189306132939</v>
+        <v>0.01538820876819236</v>
       </c>
       <c r="D16" t="n">
-        <v>0.002312640381544727</v>
+        <v>0.002752958640584714</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01713807109208184</v>
+        <v>0.01738510867018062</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01713807109208184</v>
+        <v>0.01738510867018062</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002430455191028483</v>
+        <v>0.002626696220808867</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0191976952618758</v>
+        <v>0.019496780434212</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0191976952618758</v>
+        <v>0.019496780434212</v>
       </c>
       <c r="D18" t="n">
-        <v>0.002865298265709806</v>
+        <v>0.002750891673289019</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02141704506552171</v>
+        <v>0.02175614018405347</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02141704506552171</v>
+        <v>0.02175614018405347</v>
       </c>
       <c r="D19" t="n">
-        <v>0.003569039421696624</v>
+        <v>0.003280838504331669</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02373554972458981</v>
+        <v>0.02409919825258688</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02373554972458981</v>
+        <v>0.02409919825258688</v>
       </c>
       <c r="D20" t="n">
-        <v>0.004318934487819531</v>
+        <v>0.003953195442499602</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02603350632517627</v>
+        <v>0.02640332735492696</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02603350632517627</v>
+        <v>0.02640332735492696</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004813219594738237</v>
+        <v>0.004446152934461547</v>
       </c>
     </row>
     <row r="22">
@@ -735,13 +735,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02825684402008642</v>
+        <v>0.02861636610492707</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02825684402008642</v>
+        <v>0.02861636610492707</v>
       </c>
       <c r="D22" t="n">
-        <v>0.004814433828044325</v>
+        <v>0.004438606011548159</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.03042841720898991</v>
+        <v>0.03076751762258834</v>
       </c>
       <c r="C23" t="n">
-        <v>0.03042841720898991</v>
+        <v>0.03076751762258834</v>
       </c>
       <c r="D23" t="n">
-        <v>0.004240185449006957</v>
+        <v>0.003833204684592046</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.03269627193528991</v>
+        <v>0.03301450755900329</v>
       </c>
       <c r="C24" t="n">
-        <v>0.03269627193528991</v>
+        <v>0.03301450755900329</v>
       </c>
       <c r="D24" t="n">
-        <v>0.003248080709731981</v>
+        <v>0.002786136068926201</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.03516966569226134</v>
+        <v>0.03547846376477518</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03516966569226134</v>
+        <v>0.03547846376477518</v>
       </c>
       <c r="D25" t="n">
-        <v>0.002207237568535025</v>
+        <v>0.001730434107690819</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.03794515937760282</v>
+        <v>0.03826337575495716</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03794515937760282</v>
+        <v>0.03826337575495716</v>
       </c>
       <c r="D26" t="n">
-        <v>0.001811404056729516</v>
+        <v>0.001729660476276296</v>
       </c>
     </row>
     <row r="27">
@@ -805,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.04095521337487712</v>
+        <v>0.04130160133889311</v>
       </c>
       <c r="C27" t="n">
-        <v>0.04095521337487712</v>
+        <v>0.04130160133889311</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002471988258959001</v>
+        <v>0.002866792227117366</v>
       </c>
     </row>
     <row r="28">
@@ -819,13 +819,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04416063375224358</v>
+        <v>0.04455578825335992</v>
       </c>
       <c r="C28" t="n">
-        <v>0.04416063375224358</v>
+        <v>0.04455578825335992</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00348464450288663</v>
+        <v>0.004177787357732828</v>
       </c>
     </row>
     <row r="29">
@@ -833,13 +833,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0474312867661246</v>
+        <v>0.04789020069424115</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0474312867661246</v>
+        <v>0.04789020069424115</v>
       </c>
       <c r="D29" t="n">
-        <v>0.004428825926510128</v>
+        <v>0.005337810276633276</v>
       </c>
     </row>
     <row r="30">
@@ -847,13 +847,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.05063030450847708</v>
+        <v>0.05115980217328591</v>
       </c>
       <c r="C30" t="n">
-        <v>0.05063030450847708</v>
+        <v>0.05115980217328591</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005189767913885047</v>
+        <v>0.006298435319980348</v>
       </c>
     </row>
     <row r="31">
@@ -861,13 +861,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.05375079795776069</v>
+        <v>0.05435386709832372</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05375079795776069</v>
+        <v>0.05435386709832372</v>
       </c>
       <c r="D31" t="n">
-        <v>0.005751044451351598</v>
+        <v>0.007043512167317129</v>
       </c>
     </row>
   </sheetData>
